--- a/src/lib/report/assets/default/weekly_report_xlsx.xlsx
+++ b/src/lib/report/assets/default/weekly_report_xlsx.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>{{report.project_name}} · 주간보고</t>
   </si>
@@ -34,7 +34,7 @@
     <t>{{kpi.actual}}</t>
   </si>
   <si>
-    <t>구분</t>
+    <t>업무영역 · 항목</t>
   </si>
   <si>
     <t>금주 실적</t>
@@ -43,25 +43,13 @@
     <t>차주 계획</t>
   </si>
   <si>
-    <t>금주 이슈</t>
-  </si>
-  <si>
-    <t>차주 이슈</t>
-  </si>
-  <si>
     <t>{{#rows sections}}{{.name}}</t>
   </si>
   <si>
     <t>{{.this_content}}</t>
   </si>
   <si>
-    <t>{{.next_content}}</t>
-  </si>
-  <si>
-    <t>{{.this_issue}}</t>
-  </si>
-  <si>
-    <t>{{.next_issue}}{{/rows}}</t>
+    <t>{{.next_content}}{{/rows}}</t>
   </si>
 </sst>
 </file>
@@ -466,21 +454,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="5" width="36" customWidth="1"/>
+    <col min="2" max="4" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -504,7 +490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
@@ -514,33 +500,21 @@
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" ht="75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" ht="75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
